--- a/Results/Algorithms.xlsx
+++ b/Results/Algorithms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Feri\Code Projects\DOE3\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1223B2B8-B739-462B-9011-5E101C4F3D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A66975-D72E-4C1F-88B8-49888D116D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="8295" windowWidth="29040" windowHeight="15720" xr2:uid="{929EBC79-5FD3-4E33-9375-BDDBF0127618}"/>
+    <workbookView xWindow="9355" yWindow="0" windowWidth="9920" windowHeight="10155" xr2:uid="{929EBC79-5FD3-4E33-9375-BDDBF0127618}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t>READMM</t>
   </si>
@@ -50,15 +50,6 @@
     <t>T</t>
   </si>
   <si>
-    <t>Obj</t>
-  </si>
-  <si>
-    <t>Benchmark Obj</t>
-  </si>
-  <si>
-    <t>Gap (%)</t>
-  </si>
-  <si>
     <t>Iterations (2000)</t>
   </si>
   <si>
@@ -66,6 +57,12 @@
   </si>
   <si>
     <t>Timedout</t>
+  </si>
+  <si>
+    <t>y residual</t>
+  </si>
+  <si>
+    <t>z residual</t>
   </si>
 </sst>
 </file>
@@ -76,7 +73,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,8 +81,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,12 +100,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -117,12 +116,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -134,15 +130,13 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,22 +451,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DD4800-87F8-41B9-98B5-7E668F9B4EB5}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="7" width="16.36328125" customWidth="1"/>
+    <col min="1" max="6" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="C1" s="8" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -480,330 +473,159 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="E3" s="2">
+        <v>51.73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A4" s="2"/>
+      <c r="B4" s="6">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.49</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="E4" s="2">
+        <v>133.6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A5" s="2"/>
+      <c r="B5" s="6">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.03</v>
+      </c>
+      <c r="E5" s="2">
+        <v>249.9</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>20.82</v>
+      </c>
+      <c r="E8" s="2">
+        <v>54.31</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A3" s="3">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.71230000000000004</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7077</v>
-      </c>
-      <c r="E3" s="2">
-        <f>100*ABS(C3-D3)/D3</f>
-        <v>0.64999293485941056</v>
-      </c>
-      <c r="F3" s="3">
-        <v>26.45</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2">
         <v>12</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.61219999999999997</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.60709999999999997</v>
-      </c>
-      <c r="E4" s="2">
-        <f>100*ABS(C4-D4)/D4</f>
-        <v>0.84005929830340864</v>
-      </c>
-      <c r="F4" s="3">
-        <v>104.66</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1564</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3">
+      <c r="C9" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D9" s="3">
+        <v>32.75</v>
+      </c>
+      <c r="E9" s="2">
+        <v>120.6</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2">
         <v>24</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.59489999999999998</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5867</v>
-      </c>
-      <c r="E5" s="2">
-        <f>100*ABS(C5-D5)/D5</f>
-        <v>1.3976478609169909</v>
-      </c>
-      <c r="F5" s="3">
-        <v>238.38</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1596</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A6" s="6">
+      <c r="C10" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="D10" s="3">
+        <v>47.47</v>
+      </c>
+      <c r="E10" s="2">
+        <v>305.39999999999998</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.71479999999999999</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0.69089999999999996</v>
-      </c>
-      <c r="E6" s="7">
-        <f>100*ABS(C6-D6)/D6</f>
-        <v>3.4592560428426737</v>
-      </c>
-      <c r="F6" s="6">
-        <v>186.87</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.59599999999999997</v>
-      </c>
-      <c r="E7" s="7">
-        <f t="shared" ref="E7:E8" si="0">100*ABS(C7-D7)/D7</f>
-        <v>6.7114093959731607</v>
-      </c>
-      <c r="F7" s="6">
-        <v>594.67999999999995</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1654</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
-        <v>24</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.63170000000000004</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0.57020000000000004</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" si="0"/>
-        <v>10.785689231848474</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1395</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="C9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A11" s="3">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3">
-        <v>4</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0.73319999999999996</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.7077</v>
-      </c>
-      <c r="E11" s="2">
-        <f>100*ABS(C11-D11)/D11</f>
-        <v>3.603221704111907</v>
-      </c>
-      <c r="F11" s="3">
-        <v>91.21</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0.63370000000000004</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.60709999999999997</v>
-      </c>
-      <c r="E12" s="2">
-        <f>100*ABS(C12-D12)/D12</f>
-        <v>4.3814857519354424</v>
-      </c>
-      <c r="F12" s="3">
-        <v>273.73</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.6331</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.5867</v>
-      </c>
-      <c r="E13" s="2">
-        <f>100*ABS(C13-D13)/D13</f>
-        <v>7.9086415544571329</v>
-      </c>
-      <c r="F13" s="3">
-        <v>282.29000000000002</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A14" s="6">
-        <v>6</v>
-      </c>
-      <c r="B14" s="6">
-        <v>4</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.72140000000000004</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.69089999999999996</v>
-      </c>
-      <c r="E14" s="7">
-        <f>100*ABS(C14-D14)/D14</f>
-        <v>4.4145317701548823</v>
-      </c>
-      <c r="F14" s="6">
-        <v>175.2</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6">
-        <v>12</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.61839999999999995</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0.59599999999999997</v>
-      </c>
-      <c r="E15" s="7">
-        <f t="shared" ref="E15:E16" si="1">100*ABS(C15-D15)/D15</f>
-        <v>3.7583892617449624</v>
-      </c>
-      <c r="F15" s="6">
-        <v>697.66</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6">
-        <v>24</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.63980000000000004</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.57020000000000004</v>
-      </c>
-      <c r="E16" s="7">
-        <f t="shared" si="1"/>
-        <v>12.206243423360222</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1246.67</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>9</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C1:G1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
